--- a/ml_sensitivity.xlsx
+++ b/ml_sensitivity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohan/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohan/Documents/R Studio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3ACCBDF-FD46-2343-8DF3-CB5DD9ABBEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A537A71-A33C-EA4D-B872-7848D7B5EC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{D42F9929-6BAF-3142-B273-394B4477DF29}"/>
+    <workbookView xWindow="4960" yWindow="820" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{D42F9929-6BAF-3142-B273-394B4477DF29}"/>
   </bookViews>
   <sheets>
     <sheet name="Elastic Net" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="15">
   <si>
     <t>Month</t>
   </si>
@@ -87,12 +87,15 @@
   <si>
     <t>Ridge</t>
   </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -105,13 +108,6 @@
       <color rgb="FF333333"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -134,10 +130,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1696,14 +1691,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3A098A-1684-AC43-95FF-76F8ED3F71A8}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1737,6 +1732,14 @@
       </c>
       <c r="B5">
         <v>0.499</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>0.52800000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/ml_sensitivity.xlsx
+++ b/ml_sensitivity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohan/Documents/R Studio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A537A71-A33C-EA4D-B872-7848D7B5EC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1314DABA-1C66-484E-89DC-F157687FBFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4960" yWindow="820" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{D42F9929-6BAF-3142-B273-394B4477DF29}"/>
+    <workbookView xWindow="16320" yWindow="1100" windowWidth="30240" windowHeight="18980" activeTab="5" xr2:uid="{D42F9929-6BAF-3142-B273-394B4477DF29}"/>
   </bookViews>
   <sheets>
     <sheet name="Elastic Net" sheetId="1" r:id="rId1"/>
@@ -237,10 +237,10 @@
                   <c:v>eGFR_CKD_EPI_3M</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>eGFR_CKD_EPI_12M</c:v>
+                  <c:v>eGFR_CKD_EPI_6M</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>eGFR_CKD_EPI_6M</c:v>
+                  <c:v>eGFR_CKD_EPI_12M</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>eGFR_CKD_EPI_3years</c:v>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="4" spans="1:12" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>370.745</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="5" spans="1:12" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>417.09</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>373.44799999999998</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>423.23200000000003</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>369.125</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>385.86399999999998</v>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>395.05799999999999</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>366.02</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>389.61099999999999</v>
@@ -1662,7 +1662,7 @@
     </row>
     <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1">
         <v>451.20400000000001</v>
